--- a/Roadmap Data Engineering  all Subjects2026/Paresh_75_Day_Databricks_SQL_Python_Plan.xlsx
+++ b/Roadmap Data Engineering  all Subjects2026/Paresh_75_Day_Databricks_SQL_Python_Plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pareshranjanrout/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://datapoem1-my.sharepoint.com/personal/paresh_r_datapoem_com/Documents/Desktop/-PARESH-S-6-MONTH-TRANSFORMATION-PLAN-8-LPA-30-LPA-/Roadmap Data Engineering  all Subjects2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCE87D9-6424-6142-931E-B85BB7140152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{FCCE87D9-6424-6142-931E-B85BB7140152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6747EE5-EE34-8849-8B09-44F79A1CEA48}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -363,7 +363,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,6 +377,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -442,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -458,6 +466,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -801,7 +812,7 @@
       <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="6" t="s">
